--- a/notebooks/XGBoost/predictions_ele_2019.xlsx
+++ b/notebooks/XGBoost/predictions_ele_2019.xlsx
@@ -441,12 +441,12 @@
       </c>
       <c r="C1" s="1" t="inlineStr">
         <is>
-          <t>ОПЖ_прогноз</t>
+          <t>predictions</t>
         </is>
       </c>
       <c r="D1" s="1" t="inlineStr">
         <is>
-          <t>ОПЖ_реальный</t>
+          <t>ОПЖ</t>
         </is>
       </c>
       <c r="E1" s="1" t="inlineStr">
